--- a/SearchFormulasInExcel/files_for_test/Data/Test_Input.xlsx
+++ b/SearchFormulasInExcel/files_for_test/Data/Test_Input.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
   <si>
     <t xml:space="preserve">Id</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Characteristic</t>
   </si>
   <si>
-    <t xml:space="preserve">Ala</t>
+    <t xml:space="preserve">=Ala</t>
   </si>
   <si>
     <t xml:space="preserve">Аланин</t>
@@ -160,6 +160,9 @@
     <t xml:space="preserve">special case, non-standard, most widely known as a component of collagen</t>
   </si>
   <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile</t>
   </si>
   <si>
@@ -181,16 +184,19 @@
     <t xml:space="preserve">Lys</t>
   </si>
   <si>
+    <t xml:space="preserve">=Lysine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лизин</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lysine</t>
   </si>
   <si>
-    <t xml:space="preserve">Лизин</t>
-  </si>
-  <si>
     <t xml:space="preserve">Met</t>
   </si>
   <si>
-    <t xml:space="preserve">Methionine</t>
+    <t xml:space="preserve">= Methionine</t>
   </si>
   <si>
     <t xml:space="preserve">Метионин</t>
@@ -280,7 +286,7 @@
     <t xml:space="preserve">Tryptophane</t>
   </si>
   <si>
-    <t xml:space="preserve">Tyr</t>
+    <t xml:space="preserve">=  Tyr</t>
   </si>
   <si>
     <t xml:space="preserve">Tyrosine</t>
@@ -289,7 +295,7 @@
     <t xml:space="preserve">Тирозин</t>
   </si>
   <si>
-    <t xml:space="preserve">Val</t>
+    <t xml:space="preserve">=Val</t>
   </si>
   <si>
     <t xml:space="preserve">Валин</t>
@@ -302,8 +308,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -377,7 +384,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,6 +402,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -416,7 +427,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="11.9765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.21"/>
@@ -450,7 +461,7 @@
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="e">
@@ -683,6 +694,9 @@
       <c r="A12" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="G12" s="0" t="s">
         <v>10</v>
       </c>
@@ -692,16 +706,16 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>9</v>
@@ -715,16 +729,16 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>9</v>
@@ -738,16 +752,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="C15" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>14</v>
@@ -761,16 +775,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>9</v>
@@ -784,16 +798,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>9</v>
@@ -807,16 +821,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>38</v>
@@ -830,19 +844,19 @@
         <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>10</v>
@@ -853,19 +867,19 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="0" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>69</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>10</v>
@@ -876,16 +890,16 @@
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>18</v>
@@ -899,16 +913,16 @@
         <v>10</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>18</v>
@@ -930,16 +944,16 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>9</v>
@@ -952,17 +966,17 @@
       <c r="A25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>86</v>
+      <c r="B25" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>9</v>
@@ -975,18 +989,18 @@
       <c r="A26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>89</v>
+      <c r="B26" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C26" s="2" t="n">
         <f aca="false"> 123</f>
         <v>123</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>9</v>
